--- a/AICA-L2-Batch-89-Aditi-Gulati/03_Example_Files/Outputs/02_Sample_DPDP_Workings.xlsx
+++ b/AICA-L2-Batch-89-Aditi-Gulati/03_Example_Files/Outputs/02_Sample_DPDP_Workings.xlsx
@@ -13,20 +13,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remediation" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Working paper" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trackers" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Social media" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core systems" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence log" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence log" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$1:$B$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'By domain'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$M$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Remediation'!$A$1:$M$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Working paper'!$A$1:$K$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'By domain'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$M$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Remediation'!$A$1:$M$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Working paper'!$A$1:$K$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Trackers'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Social media'!$A$1:$I$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Core systems'!$A$1:$H$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Evidence log'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Evidence log'!$A$1:$H$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -522,7 +518,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T10:20:18+00:00</t>
+          <t>2026-09-21T16:48:21+00:00</t>
         </is>
       </c>
     </row>
@@ -533,7 +529,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>8.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="6">
@@ -567,7 +563,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>58.4</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="9">
@@ -577,7 +573,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -587,7 +583,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>173</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +603,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -617,7 +613,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -627,7 +623,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -662,7 +658,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>/root/.surakshascan/evidence/Sunrise_Public_School_demonstration_20260921T102018Z.json</t>
+          <t>/root/.surakshascan/evidence/Sunrise_Public_School_demonstration_20260921T164821Z.json</t>
         </is>
       </c>
     </row>
@@ -678,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -787,19 +783,19 @@
         <v>0</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -812,19 +808,19 @@
         <v>0</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="6">
@@ -840,13 +836,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
@@ -890,45 +886,20 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="F8" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Core systems</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>13.9</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -939,7 +910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1840,22 +1811,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Children's data</t>
+          <t>Security and breach</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Social media posts do not identify an individual child</t>
+          <t>The site and its forms are served over HTTPS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>s.6(1), s.9(1), Act</t>
+          <t>s.8(5), Act; Rule 6(1)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1869,33 +1840,32 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>social</t>
+          <t>rules</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2 of 5 post(s) reviewed name a child together with a class or section, and 1 carry a student identifier</t>
+          <t>a form posts personal data to a plain http:// address</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>https://fb.example/p/1: Aarav Sharma, class 5-b
-https://ig.example/p/3: Priya Verma, class 10 a, roll no 24
-1 post(s) carry a roll or admission number</t>
+          <t>http://127.0.0.1:8931/send
+http://sunrise.example/enquiry</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Stop publishing a child's full name, class and photograph together. Use a first name only, or the class without the name, or the name without the class - and never a roll or admission number.</t>
+          <t>Install a TLS certificate, redirect HTTP to HTTPS, and confirm no form posts to an http:// action.</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1907,22 +1877,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Children's data</t>
+          <t>Security and breach</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Posts featuring children are not paid for or boosted</t>
+          <t>Reasonable security safeguards are in place and documented</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>s.9(3), Act</t>
+          <t>s.8(5), Act; Rule 6</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1930,13 +1900,13 @@
           <t>from 14 May 2027</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Gap</t>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Partly met</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1945,83 +1915,79 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>social</t>
+          <t>questionnaire</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1 boosted or paid post(s) feature students</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>https://ig.example/p/3</t>
-        </is>
-      </c>
+          <t>self-assessed: partly</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Never boost or promote a post that features students. Promote posts about facilities, admissions dates or staff instead.</t>
+          <t>Write a one-page security standard covering access control on the ERP, encryption of exports, a one-year log retention setting and a tested backup.</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Children's data</t>
+          <t>Security and breach</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Media consent is separate, granular and genuinely revocable</t>
+          <t>A personal data breach response procedure exists</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>s.6(1), s.6(4), s.9(1), Act</t>
+          <t>s.8(6), Act; Rule 7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>in force</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Partly met</t>
+          <t>from 14 May 2027</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Not assessed</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>questionnaire</t>
+          <t>rules</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>self-assessed: partly</t>
+          <t>this cannot be seen from a website; answer it in the internal-practices questionnaire</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Take media consent on its own form, channel by channel - website, social media, prospectus, press, parent groups - with a tick against each. State how a parent withdraws and the period within which the school will take the content down.</t>
+          <t>Adopt a breach procedure naming who declares a breach, the notification templates for parents and for the Board, and a breach register.</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2033,27 +1999,27 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Children's data</t>
+          <t>Retention and erasure</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Staff do not publish student data from personal accounts</t>
+          <t>A retention schedule exists and data is erased when the purpose ends</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>s.8(1), s.8(5), Act</t>
+          <t>s.8(7), Act; Rule 8</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>in force</t>
+          <t>from 14 May 2027</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -2062,7 +2028,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -2076,58 +2042,58 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>self-assessed: no</t>
+          <t>self-assessed: no. no policy text could be read, so this could not be assessed from the website</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Issue a one-page rule: student photographs and lists go out only from the school's official accounts, by a named person. Say what staff should do instead, not only what they must not do.</t>
+          <t>Set a period per record class - unsuccessful enquiries, withdrawn students, alumni, CCTV, biometric attendance - and schedule the deletion. Keep only what a records rule requires.</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Security and breach</t>
+          <t>Retention and erasure</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>The site and its forms are served over HTTPS</t>
+          <t>CCTV and biometric data are handled under a stated rule</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>s.8(5), Act; Rule 6(1)</t>
+          <t>s.8(7), Act; Rule 6, Rule 8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>in force</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Gap</t>
+          <t>from 14 May 2027</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Not assessed</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2137,55 +2103,50 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>a form posts personal data to a plain http:// address</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>http://127.0.0.1:8931/send
-http://sunrise.example/enquiry</t>
-        </is>
-      </c>
+          <t>this cannot be seen from a website; answer it in the internal-practices questionnaire</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Install a TLS certificate, redirect HTTP to HTTPS, and confirm no form posts to an http:// action.</t>
+          <t>Fix a CCTV overwrite cycle, restrict who can export footage, log every export, and confirm the biometric vendor's contract and deletion terms.</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Security and breach</t>
+          <t>Governance and grievance</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Reasonable security safeguards are in place and documented</t>
+          <t>Contact details of the person answering data questions are published</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>s.8(5), Act; Rule 6</t>
+          <t>s.5(1)(iii), s.8(9), Act; Rule 9</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>from 14 May 2027</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Not assessed</t>
+          <t>in force</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Partly met</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
@@ -2193,50 +2154,54 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>contact addresses are published but none is identifiable as the data-protection or grievance contact</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>office@sunrise.example</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Name a role - not an individual's personal mobile - publish a dedicated address such as dpo@school.edu.in on the policy page and the contact page, and route it to a monitored inbox.</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
           <t>low</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>rules</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>this cannot be seen from a website; answer it in the internal-practices questionnaire</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>Write a one-page security standard covering access control on the ERP, encryption of exports, a one-year log retention setting and a tested backup.</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Security and breach</t>
+          <t>Governance and grievance</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>A personal data breach response procedure exists</t>
+          <t>A grievance redressal mechanism with a stated response period</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>s.8(6), Act; Rule 7</t>
+          <t>s.8(10), Act; Rule 9(2)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2250,7 +2215,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2270,68 +2235,68 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Adopt a breach procedure naming who declares a breach, the notification templates for parents and for the Board, and a breach register.</t>
+          <t>Publish the grievance route and a response period, and keep a dated register of requests and outcomes.</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Retention and erasure</t>
+          <t>Governance and grievance</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>A retention schedule exists and data is erased when the purpose ends</t>
+          <t>A record of processing activities exists</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>s.8(7), Act; Rule 8</t>
+          <t>s.8(1), Act (accountability)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>from 14 May 2027</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Not assessed</t>
+          <t>in force</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Gap</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>rules</t>
+          <t>questionnaire</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>this cannot be seen from a website; answer it in the internal-practices questionnaire</t>
+          <t>self-assessed: no</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Set a period per record class - unsuccessful enquiries, withdrawn students, alumni, CCTV, biometric attendance - and schedule the deletion. Keep only what a records rule requires.</t>
+          <t>Build a register of every system holding student or staff data - ERP, transport GPS, biometric, CCTV, LMS, WhatsApp groups, exam portal - with owner, purpose, categories and vendor.</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2343,27 +2308,27 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Retention and erasure</t>
+          <t>Governance and grievance</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>CCTV and biometric data are handled under a stated rule</t>
+          <t>Staff who handle student data have been trained</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>s.8(7), Act; Rule 6, Rule 8</t>
+          <t>s.8(1), s.8(5), Act</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>from 14 May 2027</t>
+          <t>in force</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2392,34 +2357,34 @@
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Fix a CCTV overwrite cycle, restrict who can export footage, log every export, and confirm the biometric vendor's contract and deletion terms.</t>
+          <t>Run a short annual briefing for teaching and office staff, and issue a one-page rule on sharing student data.</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Governance and grievance</t>
+          <t>Processors and third parties</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Contact details of the person answering data questions are published</t>
+          <t>A written contract is in place with every data processor</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>s.5(1)(iii), s.8(9), Act; Rule 9</t>
+          <t>s.8(2), Act</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2427,9 +2392,9 @@
           <t>in force</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>Partly met</t>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Gap</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
@@ -2442,59 +2407,55 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>rules</t>
+          <t>questionnaire</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>contact addresses are published but none is identifiable as the data-protection or grievance contact</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>office@sunrise.example</t>
-        </is>
-      </c>
+          <t>self-assessed: no</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Name a role - not an individual's personal mobile - publish a dedicated address such as dpo@school.edu.in on the policy page and the contact page, and route it to a monitored inbox.</t>
+          <t>Add a data-processing addendum to each vendor agreement covering purpose limitation, security, sub-processing, breach reporting and deletion on exit.</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Governance and grievance</t>
+          <t>Processors and third parties</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>A grievance redressal mechanism with a stated response period</t>
+          <t>Third-party trackers on the website are disclosed and justified</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>s.8(10), Act; Rule 9(2)</t>
+          <t>s.5, s.6, s.9(3), Act</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>from 14 May 2027</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Not assessed</t>
+          <t>in force</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Gap</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
@@ -2502,7 +2463,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2512,592 +2473,88 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>this cannot be seen from a website; answer it in the internal-practices questionnaire</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
+          <t>2 third-party tracker host(s) load but none is named in the published policy</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>detected: connect.facebook.net, www.googletagmanager.com</t>
+        </is>
+      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Publish the grievance route and a response period, and keep a dated register of requests and outcomes.</t>
+          <t>Inventory the scripts, remove what is not needed, name the rest in the notice, and gate non-essential ones behind consent.</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Governance and grievance</t>
+          <t>Processors and third parties</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>A record of processing activities exists</t>
+          <t>Cross-border transfer position is known</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>s.8(1), Act (accountability)</t>
+          <t>s.16, Act; Rule 15</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>in force</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Gap</t>
+          <t>from 14 May 2027</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Not assessed</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>questionnaire</t>
+          <t>rules</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>self-assessed: no</t>
+          <t>this cannot be seen from a website; answer it in the internal-practices questionnaire</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Build a register of every system holding student or staff data - ERP, transport GPS, biometric, CCTV, LMS, WhatsApp groups, exam portal - with owner, purpose, categories and vendor.</t>
+          <t>Ask each vendor in writing where student data is hosted and record the answer.</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Governance and grievance</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Staff who handle student data have been trained</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>s.8(1), s.8(5), Act</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>in force</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Not assessed</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>rules</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>this cannot be seen from a website; answer it in the internal-practices questionnaire</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>Run a short annual briefing for teaching and office staff, and issue a one-page rule on sharing student data.</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Core systems</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>The student records system holds no category without a purpose</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>s.6(1) proviso, s.5(1)(i), Act</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>in force</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>systems</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2 high-harm column(s) are held: Government identifier, Health, Possible caste category, Student identifier. Each needs a stated purpose or removal</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP: column 'Aadhaar No' (Government identifier), populated in 80 of 120 rows
-Student records / ERP: column 'Category' (Possible caste category), populated in 120 of 120 rows</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>Export the student master, list every column, and write the purpose beside each. Remove or mask the columns where the purpose column stays blank, starting with identifiers and free-text remarks.</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
           <t>medium</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Core systems</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Leavers are erased from the student system when retention ends</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>s.8(7), Act; Rule 8</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>from 14 May 2027</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>systems</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>30 record(s) appear to belong to students who have left and are still held in full; self-assessed: no</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP: 30 of 120 records look inactive or left
-Student records / ERP: dates as old as 2001 appear in the data
-Learning platform: dates as old as 2026 appear in the data</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>Fix a retention period per record class, ask the vendor in writing how a record is erased, and actually run the first deletion. Keep a deletion log.</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Core systems</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Student data in the accounts is minimised and the retention conflict is recorded</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>s.6(1) proviso, s.8(7), Act</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>in force</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Not assessed</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>systems</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>this cannot be seen from a website; answer it in the internal-practices questionnaire</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>Record the conflict openly in the retention schedule: the ERP record is erased, the accounting entry is preserved under the record-keeping rules. Then ask whether the ledger needs the name at all - a receipt number reconciling to the ERP gives the same audit trail with less personal data.</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Core systems</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>The learning platform is governed as a data processor</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>s.8(1), s.8(2), Act</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>in force</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Partly met</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>systems</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>1 learning platform(s) reviewed; confirm a data-processing agreement is in place and what happens to student content when a class is archived</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Learning platform: 3 records, 7 columns
-categories held: Academic performance, Attendance, Contact, Name</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>List every learning platform actually in use, including the free ones teachers signed up for. Put a data-processing addendum in place, restrict who can create a class, and confirm what happens to student content when a class is archived.</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Processors and third parties</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>A written contract is in place with every data processor</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>s.8(2), Act</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>in force</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Not assessed</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>rules</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>this cannot be seen from a website; answer it in the internal-practices questionnaire</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>Add a data-processing addendum to each vendor agreement covering purpose limitation, security, sub-processing, breach reporting and deletion on exit.</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Processors and third parties</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Third-party trackers on the website are disclosed and justified</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>s.5, s.6, s.9(3), Act</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>in force</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>rules</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>2 third-party tracker host(s) load but none is named in the published policy</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>detected: connect.facebook.net, www.googletagmanager.com</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>Inventory the scripts, remove what is not needed, name the rest in the notice, and gate non-essential ones behind consent.</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Processors and third parties</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Cross-border transfer position is known</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>s.16, Act; Rule 15</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>from 14 May 2027</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Not assessed</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>rules</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>this cannot be seen from a website; answer it in the internal-practices questionnaire</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>Ask each vendor in writing where student data is hosted and record the answer.</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M34"/>
+  <autoFilter ref="A1:M26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3108,7 +2565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3228,7 +2685,7 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>7.9</v>
+        <v>10.1</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -3279,7 +2736,7 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>7.9</v>
+        <v>10.1</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -3301,17 +2758,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Social media posts do not identify an individual child</t>
+          <t>A privacy notice is published and reachable from the website</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Children's data</t>
+          <t>Notice and transparency</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -3321,7 +2778,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Stop publishing a child's full name, class and photograph together. Use a first name only, or the class without the name, or the name without the class - and never a roll or admission number.</t>
+          <t>Publish a DPDP notice at /privacy-policy and link it from the footer of every page, the admission enquiry form and the fee portal.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3330,11 +2787,11 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>s.6(1), s.9(1), Act</t>
+          <t>s.5, Act; Rule 3, Rules</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3352,17 +2809,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>The student records system holds no category without a purpose</t>
+          <t>A retention schedule exists and data is erased when the purpose ends</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Core systems</t>
+          <t>Retention and erasure</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -3372,25 +2829,25 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Export the student master, list every column, and write the purpose beside each. Remove or mask the columns where the purpose column stays blank, starting with identifiers and free-text remarks.</t>
+          <t>Set a period per record class - unsuccessful enquiries, withdrawn students, alumni, CCTV, biometric attendance - and schedule the deletion. Keep only what a records rule requires.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>s.6(1) proviso, s.5(1)(i), Act</t>
+          <t>s.8(7), Act; Rule 8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>in force</t>
+          <t>from 14 May 2027</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
@@ -3403,17 +2860,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>A privacy notice is published and reachable from the website</t>
+          <t>A written contract is in place with every data processor</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Notice and transparency</t>
+          <t>Processors and third parties</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -3423,20 +2880,20 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Publish a DPDP notice at /privacy-policy and link it from the footer of every page, the admission enquiry form and the fee portal.</t>
+          <t>Add a data-processing addendum to each vendor agreement covering purpose limitation, security, sub-processing, breach reporting and deletion on exit.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>s.5, Act; Rule 3, Rules</t>
+          <t>s.8(2), Act</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3454,17 +2911,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Leavers are erased from the student system when retention ends</t>
+          <t>The site and its forms are served over HTTPS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Core systems</t>
+          <t>Security and breach</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -3474,25 +2931,25 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Fix a retention period per record class, ask the vendor in writing how a record is erased, and actually run the first deletion. Keep a deletion log.</t>
+          <t>Install a TLS certificate, redirect HTTP to HTTPS, and confirm no form posts to an http:// action.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>s.8(7), Act; Rule 8</t>
+          <t>s.8(5), Act; Rule 6(1)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>from 14 May 2027</t>
+          <t>in force</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
@@ -3505,17 +2962,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>The site and its forms are served over HTTPS</t>
+          <t>Consent is collected by clear affirmative action, not assumed</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Security and breach</t>
+          <t>Consent</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -3525,20 +2982,20 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Install a TLS certificate, redirect HTTP to HTTPS, and confirm no form posts to an http:// action.</t>
+          <t>Replace any implied-consent banner with an unticked checkbox beside a link to the notice, and log the consent artefact.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>s.8(5), Act; Rule 6(1)</t>
+          <t>s.6(1), Act</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3556,17 +3013,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Consent is collected by clear affirmative action, not assumed</t>
+          <t>Student photographs and names are not published without consent</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Consent</t>
+          <t>Children's data</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -3576,7 +3033,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Replace any implied-consent banner with an unticked checkbox beside a link to the notice, and log the consent artefact.</t>
+          <t>Take a separate, revocable media consent at admission, keep a do-not-publish list, and honour it across website, brochures and social media.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3585,11 +3042,11 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>s.6(1), Act</t>
+          <t>s.6(1), s.9(1), Act</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3607,17 +3064,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Student photographs and names are not published without consent</t>
+          <t>Third-party trackers on the website are disclosed and justified</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Children's data</t>
+          <t>Processors and third parties</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -3627,7 +3084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Take a separate, revocable media consent at admission, keep a do-not-publish list, and honour it across website, brochures and social media.</t>
+          <t>Inventory the scripts, remove what is not needed, name the rest in the notice, and gate non-essential ones behind consent.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3636,11 +3093,11 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>s.6(1), s.9(1), Act</t>
+          <t>s.5, s.6, s.9(3), Act</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3658,17 +3115,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Third-party trackers on the website are disclosed and justified</t>
+          <t>A record of processing activities exists</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Processors and third parties</t>
+          <t>Governance and grievance</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -3678,20 +3135,20 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Inventory the scripts, remove what is not needed, name the rest in the notice, and gate non-essential ones behind consent.</t>
+          <t>Build a register of every system holding student or staff data - ERP, transport GPS, biometric, CCTV, LMS, WhatsApp groups, exam portal - with owner, purpose, categories and vendor.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>s.5, s.6, s.9(3), Act</t>
+          <t>s.8(1), Act (accountability)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3709,17 +3166,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>A record of processing activities exists</t>
+          <t>Only data necessary for the stated purpose is collected</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Governance and grievance</t>
+          <t>Consent</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -3729,20 +3186,20 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Build a register of every system holding student or staff data - ERP, transport GPS, biometric, CCTV, LMS, WhatsApp groups, exam portal - with owner, purpose, categories and vendor.</t>
+          <t>Review every public form field against its purpose and delete the fields that cannot be justified.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>s.8(1), Act (accountability)</t>
+          <t>s.6(1) proviso, Act</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3760,12 +3217,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Only data necessary for the stated purpose is collected</t>
+          <t>Consent records are kept and are auditable</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3780,20 +3237,20 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Review every public form field against its purpose and delete the fields that cannot be justified.</t>
+          <t>Add a dated, signed DPDP consent block to the admission form and keep a register mapping student to consent version.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>s.6(1) proviso, Act</t>
+          <t>s.6(1), s.8(1), Act</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3811,27 +3268,27 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Posts featuring children are not paid for or boosted</t>
+          <t>Contact details of the person answering data questions are published</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Children's data</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Gap</t>
+          <t>Governance and grievance</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Partly met</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Never boost or promote a post that features students. Promote posts about facilities, admissions dates or staff instead.</t>
+          <t>Name a role - not an individual's personal mobile - publish a dedicated address such as dpo@school.edu.in on the policy page and the contact page, and route it to a monitored inbox.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3840,16 +3297,16 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>s.9(3), Act</t>
+          <t>s.5(1)(iii), s.8(9), Act; Rule 9</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>from 14 May 2027</t>
+          <t>in force</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
@@ -3862,257 +3319,53 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Staff do not publish student data from personal accounts</t>
+          <t>Reasonable security safeguards are in place and documented</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Children's data</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Gap</t>
+          <t>Security and breach</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Partly met</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Issue a one-page rule: student photographs and lists go out only from the school's official accounts, by a named person. Say what staff should do instead, not only what they must not do.</t>
+          <t>Write a one-page security standard covering access control on the ERP, encryption of exports, a one-year log retention setting and a tested backup.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>s.8(1), s.8(5), Act</t>
+          <t>s.8(5), Act; Rule 6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>in force</t>
+          <t>from 14 May 2027</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Consent records are kept and are auditable</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Consent</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Add a dated, signed DPDP consent block to the admission form and keep a register mapping student to consent version.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>s.6(1), s.8(1), Act</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>in force</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>C7</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Media consent is separate, granular and genuinely revocable</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Children's data</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Partly met</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Take media consent on its own form, channel by channel - website, social media, prospectus, press, parent groups - with a tick against each. State how a parent withdraws and the period within which the school will take the content down.</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>s.6(1), s.6(4), s.9(1), Act</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>in force</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Contact details of the person answering data questions are published</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Governance and grievance</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Partly met</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Name a role - not an individual's personal mobile - publish a dedicated address such as dpo@school.edu.in on the policy page and the contact page, and route it to a monitored inbox.</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>s.5(1)(iii), s.8(9), Act; Rule 9</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>in force</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>The learning platform is governed as a data processor</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Core systems</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Partly met</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>List every learning platform actually in use, including the free ones teachers signed up for. Put a data-processing addendum in place, restrict who can create a class, and confirm what happens to student content when a class is archived.</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>s.8(1), s.8(2), Act</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>in force</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M19"/>
+  <autoFilter ref="A1:M15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4123,7 +3376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4865,22 +4118,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Publication and Social Media</t>
+          <t>Children and Safeguarding</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Is media consent taken on a separate form, rather than as a clause inside the admission form?</t>
+          <t>Is a do-not-publish list maintained and checked before a photograph goes out?</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>partly</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -4905,12 +4158,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>The media consent form itself.</t>
+          <t>The list, and whoever checks it.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>A clause bundled with admission is consent a parent cannot refuse without appearing to refuse the admission.</t>
+          <t>Some parents have reasons they should not have to explain, such as a custody arrangement.</t>
         </is>
       </c>
     </row>
@@ -4922,44 +4175,52 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Publication and Social Media</t>
+          <t>Security and Retention</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Does that consent distinguish between channels - website, social media, prospectus, press, parent groups?</t>
+          <t>Is access to the student database restricted by named user accounts rather than a shared login?</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>partly</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Demo reviewer</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
+          <t>document seen</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Reviewed by Demo reviewer on 21 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>The form, and whether it has separate ticks.</t>
+          <t>The ERP user list.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>One tick covering everything is not specific consent.</t>
+          <t>A shared 'admin' password means no audit trail exists.</t>
         </is>
       </c>
     </row>
@@ -4971,17 +4232,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Publication and Social Media</t>
+          <t>Security and Retention</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Has a parent ever withdrawn media consent, and was the content actually taken down?</t>
+          <t>Are exports of student data - Excel downloads, mark sheets, address lists - controlled and logged?</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -5003,14 +4264,10 @@
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>The withdrawal register and evidence of the takedown.</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>A revocable consent nobody has ever revoked is untested.</t>
-        </is>
-      </c>
+          <t>The export log, or the absence of one.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -5020,54 +4277,42 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Publication and Social Media</t>
+          <t>Security and Retention</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Is a do-not-publish list maintained and checked before a photograph goes out?</t>
+          <t>Are backups taken and has a restore been tested in the last year?</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Demo reviewer</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>document seen</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Reviewed by Demo reviewer on 21 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
-        </is>
-      </c>
+          <t>not verified</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>The list, and whoever checks it.</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Some parents have reasons they should not have to explain, such as a custody arrangement.</t>
-        </is>
-      </c>
+          <t>The backup schedule and the date of the last restore test.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -5077,52 +4322,44 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Publication and Social Media</t>
+          <t>Security and Retention</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Is there a written rule that student photographs and lists go out only from official school accounts?</t>
+          <t>Is there a written procedure saying who declares a data breach and who must be told?</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Demo reviewer</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>document seen</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Reviewed by Demo reviewer on 21 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
-        </is>
-      </c>
+          <t>not verified</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>The circular or staff handbook page.</t>
+          <t>The procedure and the breach register.</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Class lists in parent WhatsApp groups are the most common school data incident.</t>
+          <t>Rule 7 requires intimation to affected persons and to the Board.</t>
         </is>
       </c>
     </row>
@@ -5134,44 +4371,52 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Publication and Social Media</t>
+          <t>Security and Retention</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Has any post featuring students been boosted or paid for?</t>
+          <t>Is there a retention schedule fixing how long each class of record is kept, with the reason?</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Demo reviewer</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
+          <t>document seen</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Reviewed by Demo reviewer on 21 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>The platform's ad or promotions history.</t>
+          <t>The schedule.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Paid promotion of a post featuring children engages section 9(3) directly.</t>
+          <t>Unsuccessful enquiries and withdrawn students are the usual problem.</t>
         </is>
       </c>
     </row>
@@ -5183,52 +4428,44 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Publication and Social Media</t>
+          <t>Security and Retention</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Is every official social media account of the school known and listed, including old or branch accounts?</t>
+          <t>Has anything actually been deleted under that schedule in the last year?</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Demo reviewer</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>document seen</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Reviewed by Demo reviewer on 21 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
-        </is>
-      </c>
+          <t>not verified</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>The list of handles, checked by searching the school's name on each platform.</t>
+          <t>The deletion log.</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Abandoned accounts still carry children's photographs and nobody is watching them.</t>
+          <t>A schedule never acted on is a document, not a control.</t>
         </is>
       </c>
     </row>
@@ -5240,44 +4477,52 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Core Systems</t>
+          <t>Vendors and Governance</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Has every column in the student records system been reviewed against a stated purpose?</t>
+          <t>Does every vendor holding student data have a signed contract with data protection terms?</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Demo reviewer</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
+          <t>document seen</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Reviewed by Demo reviewer on 21 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>The export, with a purpose written beside each column.</t>
+          <t>The contracts, listed against the system register.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>The fields that accumulate unnoticed are the ones that hurt: a caste column for a return that stopped, a free-text remarks box.</t>
+          <t>Purpose limitation, security, sub-processing, breach reporting, deletion on exit.</t>
         </is>
       </c>
     </row>
@@ -5289,54 +4534,42 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Core Systems</t>
+          <t>Vendors and Governance</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Has the vendor confirmed in writing how a student record is erased, and has a deletion actually been run?</t>
+          <t>Is it known, for each vendor, where the student data is hosted?</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Demo reviewer</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>document seen</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Reviewed by Demo reviewer on 21 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
-        </is>
-      </c>
+          <t>not verified</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>The vendor's written answer and the deletion log.</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>Most school ERPs have no delete function and nobody has ever tried.</t>
-        </is>
-      </c>
+          <t>The vendor's written answer.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5346,46 +4579,50 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Core Systems</t>
+          <t>Vendors and Governance</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Can the school produce, export or delete one named student's full record on request?</t>
+          <t>Has a person been named to answer data protection questions, with a published address that is monitored?</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>partly</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Demo reviewer</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
+          <t>document seen</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Reviewed by Demo reviewer on 21 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>A live demonstration on a record the reviewer picks.</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>This is what sections 11 and 12 require in practice. If the system cannot do it, the right cannot be honoured.</t>
-        </is>
-      </c>
+          <t>The published address and evidence that mail to it is read.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5395,17 +4632,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Core Systems</t>
+          <t>Vendors and Governance</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Does the retention schedule state that a leaver erased from the ERP still exists in the books of account?</t>
+          <t>Does the management committee receive a periodic report on data protection?</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -5427,12 +4664,12 @@
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>The retention schedule.</t>
+          <t>Minutes referring to it.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Otherwise the school tells a parent the data is gone when it is not.</t>
+          <t>Accountability sits with the Data Fiduciary, which is the institution, not the IT vendor.</t>
         </is>
       </c>
     </row>
@@ -5444,17 +4681,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Core Systems</t>
+          <t>Vendors and Governance</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Do the accounts hold anything about a student beyond the name and the receipt?</t>
+          <t>When a vendor contract ends, is deletion of the school's data confirmed in writing?</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -5476,14 +4713,10 @@
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>The fee ledger structure.</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Address, contact and class details do not need to be posted into the books.</t>
-        </is>
-      </c>
+          <t>The last exit confirmation, if any.</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5493,17 +4726,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Core Systems</t>
+          <t>Vendors and Governance</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Is every learning platform in use listed, including free ones teachers signed up for themselves?</t>
+          <t>Are the ERP's integrations known - SMS gateway, payment gateway, biometric device, transport GPS?</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -5525,630 +4758,17 @@
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>The list, checked by asking the teaching staff rather than the IT vendor.</t>
+          <t>The integrations or API settings page of the ERP.</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Unapproved classes are the ones nobody can close when the teacher leaves.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Q27</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Core Systems</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Is there a data-processing agreement with the learning platform provider, and is it known what happens to student content when a class is archived?</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>The agreement and the provider's retention terms.</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Q28</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Core Systems</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Are the ERP's integrations known - SMS gateway, payment gateway, biometric device, transport GPS?</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>The integrations or API settings page of the ERP.</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
           <t>Each integration is a further processor receiving parent numbers or child data, usually enabled once and never reviewed.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Q29</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Security and Retention</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Is access to the student database restricted by named user accounts rather than a shared login?</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>The ERP user list.</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>A shared 'admin' password means no audit trail exists.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Q30</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Security and Retention</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Are exports of student data - Excel downloads, mark sheets, address lists - controlled and logged?</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>The export log, or the absence of one.</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Q31</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Security and Retention</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Are backups taken and has a restore been tested in the last year?</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>The backup schedule and the date of the last restore test.</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Q32</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Security and Retention</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Is there a written procedure saying who declares a data breach and who must be told?</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>The procedure and the breach register.</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Rule 7 requires intimation to affected persons and to the Board.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Q33</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Security and Retention</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Is there a retention schedule fixing how long each class of record is kept, with the reason?</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>The schedule.</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Unsuccessful enquiries and withdrawn students are the usual problem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Q34</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Security and Retention</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Has anything actually been deleted under that schedule in the last year?</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>The deletion log.</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>A schedule never acted on is a document, not a control.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Q35</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Vendors and Governance</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Does every vendor holding student data have a signed contract with data protection terms?</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>The contracts, listed against the system register.</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Purpose limitation, security, sub-processing, breach reporting, deletion on exit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Q36</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Vendors and Governance</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Is it known, for each vendor, where the student data is hosted?</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>The vendor's written answer.</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Q37</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Vendors and Governance</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Has a person been named to answer data protection questions, with a published address that is monitored?</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>The published address and evidence that mail to it is read.</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Q38</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Vendors and Governance</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Does the management committee receive a periodic report on data protection?</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>Minutes referring to it.</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>Accountability sits with the Data Fiduciary, which is the institution, not the IT vendor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Q39</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Vendors and Governance</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>When a vendor contract ends, is deletion of the school's data confirmed in writing?</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>not verified</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>The last exit confirmation, if any.</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K40"/>
+  <autoFilter ref="A1:K27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6289,1341 +4909,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="66" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Posted</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>What was found</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Identifiers</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Boosted</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Caption</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>https://fb.example/p/1</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>celebrates an individual achievement, which is a promotional purpose and sits outside the Fourth Schedule exemption; names a child together with a class or section, which identifies and locates a specific student</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Aarav Sharma, class 5-b</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>export</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Congratulations Aarav Sharma of Class 5-B on winning the district quiz! So proud of you.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>https://fb.example/p/2</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>export</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Independence Day celebrations at our school. A wonderful morning.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>instagram</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>https://ig.example/p/3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>carries a roll, admission or student identifier, which should never appear in a public post; names a child together with a class or section, which identifies and locates a specific student; is a paid or boosted post featuring children, which moves it towards the targeted-advertising prohibition in s.9(3)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Priya Verma, class 10 a, roll no 24</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>export</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Well done Priya Verma, Class 10 A, Roll No 24, for topping the pre-board.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>https://fb.example/p/4</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>gives a class or section, which narrows the child to a small group even without a name</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>class viii</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>export</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Class VIII went on a field trip to the science museum today.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>instagram</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>https://ig.example/p/5</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>export</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Admissions open for the next session. Visit our campus to know more.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I6"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="66" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Populated</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Rows</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Fill %</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Why it matters</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Admission No</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Enrolment</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Student Name</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>DOB</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Date of birth</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Date of birth plus a name is what makes a child's record re-identifiable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Class or roll</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Class or roll</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Father Name</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Parent identity</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Parents are Data Principals in their own right.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Father Mobile</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Parent phone numbers are the field most often exported and forwarded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Mother Mobile</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Parent phone numbers are the field most often exported and forwarded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Address</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Home address</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>An address plus a child's name discloses where the child lives.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Pincode</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Home address</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>An address plus a child's name discloses where the child lives.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Aadhaar No</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Government identifier</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Aadhaar should not be held unless a statute requires it. Record the purpose and mask the number at rest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>APAAR ID</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Student identifier</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>APAAR/PEN is a national identifier. Confirm the statutory basis and who it is shared with.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Possible caste category</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Collected for government returns. It should not be visible to teachers or exportable with the class list.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Blood Group</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Health</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Health data needs a narrow purpose and tight access.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Medical Notes</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Health</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Health data needs a narrow purpose and tight access.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Photo Path</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Photograph</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>A photograph is personal data and feeds the media-consent question.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Bank A/c No</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Bank particulars usually belong to a parent, not the student.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>IFSC</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Bank particulars usually belong to a parent, not the student.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Transport Pickup Point</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>A pickup point plus a name locates a child at a known time each day.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Record status</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Not personal data in itself, but it is what makes a leaver findable for deletion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Date of Admission</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Enrolment</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Total Fee</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Fee and payment</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Fee data is commercial administration, which is harder to bring inside the Fourth Schedule's 'academic activities'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Student records / ERP</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>erp_export.csv</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Marks Obtained</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Academic performance</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Publishing or sharing this beyond the school needs its own basis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Learning platform</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>lms_classroom.csv</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Class Name</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Learning platform</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>lms_classroom.csv</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Student Name</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Learning platform</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>lms_classroom.csv</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Student Email</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Used for circulars; confirm it is not shared on.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Learning platform</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>lms_classroom.csv</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Attendance</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Attendance</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Learning platform</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>lms_classroom.csv</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Grade</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Academic performance</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Publishing or sharing this beyond the school needs its own basis.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:H29"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/AICA-L2-Batch-89-Aditi-Gulati/03_Example_Files/Outputs/02_Sample_DPDP_Workings.xlsx
+++ b/AICA-L2-Batch-89-Aditi-Gulati/03_Example_Files/Outputs/02_Sample_DPDP_Workings.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T16:48:21+00:00</t>
+          <t>2026-09-23T12:59:59+00:00</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>/root/.surakshascan/evidence/Sunrise_Public_School_demonstration_20260921T164821Z.json</t>
+          <t>/root/.surakshascan/evidence/Sunrise_Public_School_demonstration_20260923T125959Z.json</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Reviewed by Demo reviewer on 21 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
+          <t>Reviewed by Demo reviewer on 23 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Reviewed by Demo reviewer on 21 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
+          <t>Reviewed by Demo reviewer on 23 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Reviewed by Demo reviewer on 21 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
+          <t>Reviewed by Demo reviewer on 23 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Reviewed by Demo reviewer on 21 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
+          <t>Reviewed by Demo reviewer on 23 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Reviewed by Demo reviewer on 21 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
+          <t>Reviewed by Demo reviewer on 23 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Reviewed by Demo reviewer on 21 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
+          <t>Reviewed by Demo reviewer on 23 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Reviewed by Demo reviewer on 21 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
+          <t>Reviewed by Demo reviewer on 23 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Reviewed by Demo reviewer on 21 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
+          <t>Reviewed by Demo reviewer on 23 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Reviewed by Demo reviewer on 21 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
+          <t>Reviewed by Demo reviewer on 23 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Reviewed by Demo reviewer on 21 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
+          <t>Reviewed by Demo reviewer on 23 September 2026. The evidence described for this line was inspected and the answer recorded above reflects it. No further exception was noted.</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
